--- a/permission_definitions.xlsx
+++ b/permission_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\configuration\master-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8270F8EB-ABE9-402B-A09F-E5E16A1FAF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA034B9-EA2D-4D63-BDE7-38818AA435D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2535" yWindow="1950" windowWidth="22230" windowHeight="11910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="810" windowWidth="25560" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="permission_definitions_new" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5759" uniqueCount="1491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5781" uniqueCount="1495">
   <si>
     <t>#SERVICE_METHOD</t>
   </si>
@@ -4498,6 +4498,18 @@
   </si>
   <si>
     <t>org.phoenixctms.ctsms.service.trial.TrialService.renderEcrfSpecification</t>
+  </si>
+  <si>
+    <t>org.phoenixctms.ctsms.service.shared.SearchService.formatCriterionText</t>
+  </si>
+  <si>
+    <t>org.phoenixctms.ctsms.service.shared.SearchService.parseCriterionText</t>
+  </si>
+  <si>
+    <t>org.phoenixctms.ctsms.service.shared.SearchService.formatCriterionText:module</t>
+  </si>
+  <si>
+    <t>org.phoenixctms.ctsms.service.shared.SearchService.parseCriterionText:module</t>
   </si>
 </sst>
 </file>
@@ -5366,7 +5378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1143"/>
+  <dimension ref="A1:I1147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="110.28515625" bestFit="1" customWidth="1"/>
@@ -24315,63 +24327,81 @@
     </row>
     <row r="1103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
-        <v>1299</v>
+        <v>1491</v>
       </c>
       <c r="C1103" t="s">
-        <v>1258</v>
+        <v>1209</v>
       </c>
       <c r="E1103" t="s">
-        <v>1259</v>
+        <v>1171</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>1493</v>
       </c>
       <c r="I1103" t="s">
-        <v>1260</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="1104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>1299</v>
-      </c>
-      <c r="G1104" t="s">
-        <v>1261</v>
-      </c>
-      <c r="H1104" t="s">
-        <v>1461</v>
+        <v>1491</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>1493</v>
       </c>
       <c r="I1104" t="s">
-        <v>1463</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="1105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
-        <v>1300</v>
+        <v>1492</v>
       </c>
       <c r="C1105" t="s">
-        <v>1258</v>
+        <v>1209</v>
       </c>
       <c r="E1105" t="s">
-        <v>1259</v>
+        <v>1171</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>1494</v>
       </c>
       <c r="I1105" t="s">
-        <v>1274</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="1106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>1300</v>
-      </c>
-      <c r="G1106" t="s">
-        <v>1261</v>
-      </c>
-      <c r="H1106" t="s">
-        <v>1262</v>
+        <v>1492</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>1494</v>
       </c>
       <c r="I1106" t="s">
-        <v>1301</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="1107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>1411</v>
+        <v>1299</v>
       </c>
       <c r="C1107" t="s">
         <v>1258</v>
@@ -24380,29 +24410,26 @@
         <v>1259</v>
       </c>
       <c r="I1107" t="s">
-        <v>1274</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="1108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>1411</v>
+        <v>1299</v>
       </c>
       <c r="G1108" t="s">
         <v>1261</v>
       </c>
       <c r="H1108" t="s">
-        <v>1262</v>
+        <v>1461</v>
       </c>
       <c r="I1108" t="s">
-        <v>1301</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>20</v>
+        <v>1300</v>
       </c>
       <c r="C1109" t="s">
         <v>1258</v>
@@ -24411,29 +24438,26 @@
         <v>1259</v>
       </c>
       <c r="I1109" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B1110" t="s">
-        <v>20</v>
+        <v>1300</v>
       </c>
       <c r="G1110" t="s">
         <v>1261</v>
       </c>
       <c r="H1110" t="s">
-        <v>1271</v>
+        <v>1262</v>
       </c>
       <c r="I1110" t="s">
-        <v>542</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="1111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
-        <v>1303</v>
+        <v>1411</v>
       </c>
       <c r="C1111" t="s">
         <v>1258</v>
@@ -24442,54 +24466,60 @@
         <v>1259</v>
       </c>
       <c r="I1111" t="s">
-        <v>1260</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
-        <v>1303</v>
+        <v>1411</v>
       </c>
       <c r="G1112" t="s">
         <v>1261</v>
       </c>
       <c r="H1112" t="s">
-        <v>1461</v>
+        <v>1262</v>
       </c>
       <c r="I1112" t="s">
-        <v>1464</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="1113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>1304</v>
+        <v>1302</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>20</v>
       </c>
       <c r="C1113" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="E1113" t="s">
         <v>1259</v>
       </c>
       <c r="I1113" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="1114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
-        <v>1304</v>
+        <v>1302</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>20</v>
       </c>
       <c r="G1114" t="s">
         <v>1261</v>
       </c>
       <c r="H1114" t="s">
-        <v>1461</v>
+        <v>1271</v>
       </c>
       <c r="I1114" t="s">
-        <v>1465</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="C1115" t="s">
         <v>1258</v>
@@ -24498,82 +24528,82 @@
         <v>1259</v>
       </c>
       <c r="I1115" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="1116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C1116" t="s">
-        <v>1255</v>
-      </c>
-      <c r="E1116" t="s">
-        <v>1259</v>
+        <v>1303</v>
+      </c>
+      <c r="G1116" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H1116" t="s">
+        <v>1461</v>
       </c>
       <c r="I1116" t="s">
-        <v>1264</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="C1117" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E1117" t="s">
         <v>1259</v>
       </c>
       <c r="I1117" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="1118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="G1118" t="s">
         <v>1261</v>
       </c>
       <c r="H1118" t="s">
-        <v>1262</v>
+        <v>1461</v>
       </c>
       <c r="I1118" t="s">
-        <v>1308</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="C1119" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="E1119" t="s">
         <v>1259</v>
       </c>
       <c r="I1119" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="1120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>1309</v>
-      </c>
-      <c r="G1120" t="s">
-        <v>1261</v>
-      </c>
-      <c r="H1120" t="s">
-        <v>1262</v>
+        <v>1306</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>1259</v>
       </c>
       <c r="I1120" t="s">
-        <v>81</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="1121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="C1121" t="s">
         <v>1258</v>
@@ -24582,12 +24612,12 @@
         <v>1259</v>
       </c>
       <c r="I1121" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="1122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="G1122" t="s">
         <v>1261</v>
@@ -24596,12 +24626,12 @@
         <v>1262</v>
       </c>
       <c r="I1122" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="1123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="C1123" t="s">
         <v>1255</v>
@@ -24610,12 +24640,12 @@
         <v>1259</v>
       </c>
       <c r="I1123" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="1124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="G1124" t="s">
         <v>1261</v>
@@ -24624,12 +24654,12 @@
         <v>1262</v>
       </c>
       <c r="I1124" t="s">
-        <v>1099</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C1125" t="s">
         <v>1258</v>
@@ -24638,29 +24668,26 @@
         <v>1259</v>
       </c>
       <c r="I1125" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="1126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="G1126" t="s">
         <v>1261</v>
       </c>
       <c r="H1126" t="s">
-        <v>1271</v>
+        <v>1262</v>
       </c>
       <c r="I1126" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="1127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>20</v>
+        <v>1312</v>
       </c>
       <c r="C1127" t="s">
         <v>1255</v>
@@ -24669,29 +24696,26 @@
         <v>1259</v>
       </c>
       <c r="I1127" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="1128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>20</v>
+        <v>1312</v>
       </c>
       <c r="G1128" t="s">
         <v>1261</v>
       </c>
       <c r="H1128" t="s">
-        <v>1271</v>
+        <v>1262</v>
       </c>
       <c r="I1128" t="s">
-        <v>542</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="1129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="C1129" t="s">
         <v>1258</v>
@@ -24700,26 +24724,29 @@
         <v>1259</v>
       </c>
       <c r="I1129" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="1130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="G1130" t="s">
         <v>1261</v>
       </c>
       <c r="H1130" t="s">
-        <v>1262</v>
+        <v>1271</v>
       </c>
       <c r="I1130" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="1131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
-        <v>1318</v>
+        <v>1315</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>20</v>
       </c>
       <c r="C1131" t="s">
         <v>1255</v>
@@ -24728,26 +24755,29 @@
         <v>1259</v>
       </c>
       <c r="I1131" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="1132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
-        <v>1318</v>
+        <v>1315</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>20</v>
       </c>
       <c r="G1132" t="s">
         <v>1261</v>
       </c>
       <c r="H1132" t="s">
-        <v>1262</v>
+        <v>1271</v>
       </c>
       <c r="I1132" t="s">
-        <v>1317</v>
+        <v>542</v>
       </c>
     </row>
     <row r="1133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C1133" t="s">
         <v>1258</v>
@@ -24756,26 +24786,26 @@
         <v>1259</v>
       </c>
       <c r="I1133" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="G1134" t="s">
         <v>1261</v>
       </c>
       <c r="H1134" t="s">
-        <v>1457</v>
+        <v>1262</v>
       </c>
       <c r="I1134" t="s">
-        <v>1458</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="1135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C1135" t="s">
         <v>1255</v>
@@ -24784,26 +24814,26 @@
         <v>1259</v>
       </c>
       <c r="I1135" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="G1136" t="s">
         <v>1261</v>
       </c>
       <c r="H1136" t="s">
-        <v>1457</v>
+        <v>1262</v>
       </c>
       <c r="I1136" t="s">
-        <v>1459</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="1137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C1137" t="s">
         <v>1258</v>
@@ -24812,26 +24842,26 @@
         <v>1259</v>
       </c>
       <c r="I1137" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="G1138" t="s">
         <v>1261</v>
       </c>
       <c r="H1138" t="s">
-        <v>1262</v>
+        <v>1457</v>
       </c>
       <c r="I1138" t="s">
-        <v>936</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C1139" t="s">
         <v>1255</v>
@@ -24840,80 +24870,136 @@
         <v>1259</v>
       </c>
       <c r="I1139" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="G1140" t="s">
         <v>1261</v>
       </c>
       <c r="H1140" t="s">
-        <v>1262</v>
+        <v>1457</v>
       </c>
       <c r="I1140" t="s">
-        <v>936</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C1141" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D1141" t="s">
-        <v>1170</v>
+        <v>1258</v>
       </c>
       <c r="E1141" t="s">
-        <v>1171</v>
-      </c>
-      <c r="F1141" t="s">
-        <v>1325</v>
+        <v>1259</v>
       </c>
       <c r="I1141" t="s">
-        <v>1172</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="1142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
-        <v>1323</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1142" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D1142" t="s">
-        <v>1170</v>
-      </c>
-      <c r="E1142" t="s">
-        <v>1173</v>
-      </c>
-      <c r="F1142" t="s">
-        <v>1325</v>
+        <v>1321</v>
+      </c>
+      <c r="G1142" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H1142" t="s">
+        <v>1262</v>
       </c>
       <c r="I1142" t="s">
-        <v>1174</v>
+        <v>936</v>
       </c>
     </row>
     <row r="1143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I1143" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1144" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G1144" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H1144" t="s">
+        <v>1262</v>
+      </c>
+      <c r="I1144" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1145" t="s">
         <v>1323</v>
       </c>
-      <c r="C1143" t="s">
+      <c r="C1145" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D1145" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I1145" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1146" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D1146" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I1146" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1147" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C1147" t="s">
         <v>1326</v>
       </c>
-      <c r="E1143" t="s">
+      <c r="E1147" t="s">
         <v>1225</v>
       </c>
-      <c r="F1143" t="s">
+      <c r="F1147" t="s">
         <v>1327</v>
       </c>
-      <c r="I1143" t="s">
+      <c r="I1147" t="s">
         <v>1328</v>
       </c>
     </row>
